--- a/data/trans_orig/P79A6_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A6_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>36730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>44303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>43885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>53083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>77958</t>
+          <t>90780</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71607</t>
+          <t>83705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82169</t>
+          <t>95666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>56795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>87701</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87701</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87701</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>75577</t>
+          <t>84269</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67943</t>
+          <t>74641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80331</t>
+          <t>89670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75700</t>
+          <t>87392</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>75667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80982</t>
+          <t>93433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>151276</t>
+          <t>171660</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138372</t>
+          <t>158743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158984</t>
+          <t>180997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>24981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33203</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>94661</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>94661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>94661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>100648</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>195308</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>195308</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>195308</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>41478</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31459</t>
+          <t>35669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>45411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37033</t>
+          <t>46686</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>51214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>88164</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>77637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80562</t>
+          <t>94506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42388</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>53408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87512</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73739</t>
+          <t>88734</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66170</t>
+          <t>79562</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>95106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100196</t>
+          <t>113623</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>101626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108265</t>
+          <t>121985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>173935</t>
+          <t>202357</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161508</t>
+          <t>188464</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184488</t>
+          <t>213429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35339</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>34336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>59301</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>104863</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>104863</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86821</t>
+          <t>104863</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125716</t>
+          <t>142902</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125716</t>
+          <t>142902</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125716</t>
+          <t>142902</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212537</t>
+          <t>247765</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212537</t>
+          <t>247765</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212537</t>
+          <t>247765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>220010</t>
+          <t>256037</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>207996</t>
+          <t>242453</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229921</t>
+          <t>266812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>257146</t>
+          <t>296924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238496</t>
+          <t>279280</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>270105</t>
+          <t>310830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>477156</t>
+          <t>552961</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>455883</t>
+          <t>533348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>493374</t>
+          <t>569764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70549</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65952</t>
+          <t>77678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>114094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
